--- a/tests/fixtures/17_excel_template_invoice/data-export-control.xlsx
+++ b/tests/fixtures/17_excel_template_invoice/data-export-control.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -722,126 +722,127 @@
       <c r="F10" s="2" t="n"/>
       <c r="G10" s="2" t="n"/>
     </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>table:</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B12" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>HEADER</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>line.description</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>line.qty</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>line.unit_price</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>line.amount</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="6" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="5" t="n"/>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>Service fee</t>
         </is>
       </c>
-      <c r="E12" s="5" t="n">
+      <c r="E13" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F12" s="5" t="n">
+      <c r="F13" s="5" t="n">
         <v>200</v>
       </c>
-      <c r="G12" s="5" t="n">
+      <c r="G13" s="5" t="n">
         <v>200</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="7" t="n"/>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="8" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="7" t="n"/>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>Labor: 5 hours at $75/hr</t>
         </is>
       </c>
-      <c r="E13" s="7" t="n">
+      <c r="E14" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="F13" s="7" t="n">
+      <c r="F14" s="7" t="n">
         <v>75</v>
       </c>
-      <c r="G13" s="7" t="n">
+      <c r="G14" s="7" t="n">
         <v>375</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="6" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="5" t="n"/>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>New client discount</t>
         </is>
       </c>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n">
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n">
         <v>-50</v>
       </c>
-      <c r="G14" s="5" t="n">
+      <c r="G15" s="5" t="n">
         <v>-50</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="9" t="n"/>
-      <c r="B15" s="9" t="n"/>
-      <c r="C15" s="10" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="9" t="n"/>
+      <c r="B16" s="9" t="n"/>
+      <c r="C16" s="10" t="inlineStr">
         <is>
           <t>FOOTER</t>
         </is>
       </c>
-      <c r="D15" s="9" t="n">
+      <c r="D16" s="9" t="n">
         <v>525</v>
       </c>
-      <c r="E15" s="9" t="n">
+      <c r="E16" s="9" t="n">
         <v>0.0425</v>
       </c>
-      <c r="F15" s="9" t="n">
+      <c r="F16" s="9" t="n">
         <v>22.3125</v>
       </c>
-      <c r="G15" s="9" t="n">
+      <c r="G16" s="9" t="n">
         <v>547.3125</v>
       </c>
     </row>
